--- a/data/output/workbook/2026-07-10.xlsx
+++ b/data/output/workbook/2026-07-10.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10 14:32</t>
+          <t>2026-07-10 15:46</t>
         </is>
       </c>
     </row>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6506000000000001</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-186</v>
+        <v>-177</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>170</v>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 64.0% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8898,17 +8898,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6058</v>
+        <v>0.6335999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-154</v>
+        <v>-173</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8964,17 +8964,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6335999999999999</v>
+        <v>0.6166</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-173</v>
+        <v>-161</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6117</v>
+        <v>0.5977</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-158</v>
+        <v>-149</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9101,32 +9101,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.5601</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-217</v>
+        <v>-127</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -217). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9167,32 +9167,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5694</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-132</v>
+        <v>-190</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 65.6% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-165</v>
+        <v>-164</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>138</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9294,17 +9294,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5892999999999999</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-143</v>
+        <v>-179</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9360,37 +9360,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Portland Fire @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5762</v>
+        <v>0.1840000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-136</v>
+        <v>443</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>115</v>
+        <v>614</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 18.4% (fair +443). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9426,17 +9426,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9446,17 +9446,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5714</v>
+        <v>0.6298</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-133</v>
+        <v>-170</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 63.0% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9497,12 +9497,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5923</v>
+        <v>0.5801000000000001</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9558,37 +9558,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.1925</v>
+        <v>0.5564</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>419</v>
+        <v>-125</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>525</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 19.2% (fair +419). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5364</v>
+        <v>0.5712</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-116</v>
+        <v>-133</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9705,22 +9705,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4306</v>
+        <v>0.5717</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>132</v>
+        <v>-133</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 57.2% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9761,12 +9761,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9776,17 +9776,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5948</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>-147</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9822,17 +9822,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9842,17 +9842,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5686</v>
+        <v>0.5749</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-132</v>
+        <v>-135</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9888,37 +9888,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5377000000000001</v>
+        <v>0.4399</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-116</v>
+        <v>127</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.288</v>
+        <v>0.5179</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>247</v>
+        <v>-107</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 28.8% (fair +247). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10020,37 +10020,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Dallas Wings @ Toronto Tempo</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Toronto Tempo</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5469999999999999</v>
+        <v>0.288</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-121</v>
+        <v>247</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 28.8% (fair +247). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10091,32 +10091,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury @ Las Vegas Aces</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.2169</v>
+        <v>0.5305</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>361</v>
+        <v>-113</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>426</v>
+        <v>117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 21.7% (fair +361). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10157,32 +10157,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Over 177.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.5735</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>114</v>
+        <v>-134</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 57.4% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10218,17 +10218,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10238,17 +10238,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.62</v>
+        <v>0.4658</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-163</v>
+        <v>115</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-122</v>
+        <v>144</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10284,17 +10284,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5291</v>
+        <v>0.5062</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-112</v>
+        <v>-103</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10350,37 +10350,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>New York Liberty @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5719</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-116</v>
+        <v>-134</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10416,12 +10416,12 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10431,22 +10431,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3942</v>
+        <v>0.5162</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>154</v>
+        <v>-107</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.4589</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5411</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-108</v>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10775,17 +10775,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5236</v>
+        <v>0.5092</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-106</v>
+        <v>105</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10841,17 +10841,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.39</v>
+        <v>0.4908</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3883</v>
+        <v>0.4023</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10977,13 +10977,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6117</v>
+        <v>0.5977</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-158</v>
+        <v>-149</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11043,13 +11043,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4348</v>
+        <v>0.4251</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5652</v>
+        <v>0.5749</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-130</v>
+        <v>-135</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-117</v>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11175,10 +11175,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5762</v>
+        <v>0.5717</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-136</v>
+        <v>-133</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>115</v>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.2% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11241,10 +11241,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4238</v>
+        <v>0.4283</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>105</v>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.8% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11307,13 +11307,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4306</v>
+        <v>0.4399</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5694</v>
+        <v>0.5601</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-132</v>
+        <v>-127</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5333</v>
+        <v>0.5342</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-144</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.4658</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11571,13 +11571,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4077</v>
+        <v>0.4052</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11637,13 +11637,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5923</v>
+        <v>0.5948</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-145</v>
+        <v>-147</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11703,13 +11703,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5649</v>
+        <v>0.5617</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11769,10 +11769,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4351</v>
+        <v>0.4383</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11835,13 +11835,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4227</v>
+        <v>0.4149</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11901,13 +11901,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5773</v>
+        <v>0.5851</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-137</v>
+        <v>-141</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-138</v>
+        <v>-134</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11967,10 +11967,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4107</v>
+        <v>0.4199</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>108</v>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5892999999999999</v>
+        <v>0.5801000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-143</v>
+        <v>-138</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4162</v>
+        <v>0.4243</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>138</v>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5838</v>
+        <v>0.5757</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-140</v>
+        <v>-136</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12231,13 +12231,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5262</v>
+        <v>0.5278</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4738</v>
+        <v>0.4722</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>104</v>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5187</v>
+        <v>0.5205</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>108</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.0% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12429,13 +12429,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4813</v>
+        <v>0.4795</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.0% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5727</v>
+        <v>0.5726</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>-134</v>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4273</v>
+        <v>0.4274</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>134</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4696</v>
+        <v>0.4683</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>108</v>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12693,13 +12693,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5304</v>
+        <v>0.5317</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4636</v>
+        <v>0.4821</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>113</v>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12825,13 +12825,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5364</v>
+        <v>0.5179</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-116</v>
+        <v>-107</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12855,7 +12855,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3494</v>
+        <v>0.3604</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 36.0% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6506000000000001</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-186</v>
+        <v>-177</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>170</v>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 64.0% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4528</v>
+        <v>0.4524</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5472</v>
+        <v>0.5476</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>-121</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13155,13 +13155,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5714</v>
+        <v>0.5712</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>-133</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13221,13 +13221,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4286</v>
+        <v>0.4288</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>133</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3942</v>
+        <v>0.3834</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>180</v>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13353,13 +13353,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6058</v>
+        <v>0.6166</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-154</v>
+        <v>-161</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13419,13 +13419,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4222</v>
+        <v>0.4252</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13485,10 +13485,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5778</v>
+        <v>0.5748</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>-138</v>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13551,13 +13551,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.315</v>
+        <v>0.3443</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 31.5% (fair +217). Your call.</t>
+          <t>Model 34.4% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13617,13 +13617,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-217</v>
+        <v>-190</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 68.5% (fair -217). Your call.</t>
+          <t>Model 65.6% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13683,13 +13683,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3775</v>
+        <v>0.3785</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-165</v>
+        <v>-164</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>138</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3587399999999999</v>
+        <v>0.25926</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>179</v>
+        <v>286</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>144</v>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 25.9% (fair +286). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6412600000000001</v>
+        <v>0.74074</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-179</v>
+        <v>-286</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13947,13 +13947,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5564</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-114</v>
+        <v>-125</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14013,13 +14013,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.467</v>
+        <v>0.4436</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14079,10 +14079,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4312</v>
+        <v>0.4394</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>138</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5688</v>
+        <v>0.5606</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-132</v>
+        <v>-128</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-141</v>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5206999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-109</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4793</v>
+        <v>0.4788</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>109</v>
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5065</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-116</v>
+        <v>-103</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14409,13 +14409,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4631999999999999</v>
+        <v>0.4935</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>110</v>
+        <v>-104</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4293</v>
+        <v>0.4251</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5707</v>
+        <v>0.5749</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-133</v>
+        <v>-135</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14735,10 +14735,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5152</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14799,10 +14799,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4803</v>
+        <v>0.4848</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4201</v>
+        <v>0.4195</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>138</v>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 41.9% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5799</v>
+        <v>0.5805</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>-138</v>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.365</v>
+        <v>0.3631</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.635</v>
+        <v>0.6369</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5069</v>
+        <v>0.5063</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>-103</v>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15183,7 +15183,7 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4932</v>
+        <v>0.4937</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>103</v>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3504</v>
+        <v>0.3379</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>163</v>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +185). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6496</v>
+        <v>0.6621</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-185</v>
+        <v>-196</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-163</v>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -185). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15451,7 +15451,7 @@
         <v>114</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15507,17 +15507,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4952</v>
+        <v>0.5305</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>102</v>
+        <v>-113</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-110</v>
+        <v>117</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15573,14 +15573,14 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4182</v>
+        <v>0.4695</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>115</v>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15643,13 +15643,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5873</v>
+        <v>0.5859</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-142</v>
+        <v>-141</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-170</v>
+        <v>-165</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15709,10 +15709,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4127</v>
+        <v>0.4141</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>145</v>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15775,13 +15775,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4345</v>
+        <v>0.4338</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15841,13 +15841,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5655</v>
+        <v>0.5662</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-130</v>
+        <v>-131</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-130</v>
+        <v>-138</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15907,10 +15907,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5085</v>
+        <v>0.5099</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>105</v>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4915</v>
+        <v>0.4901</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16039,10 +16039,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3765</v>
+        <v>0.3801</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>160</v>
@@ -16069,7 +16069,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6234999999999999</v>
+        <v>0.6199</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-170</v>
+        <v>-160</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -166). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16171,13 +16171,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5933999999999999</v>
+        <v>0.5977</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-146</v>
+        <v>-149</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16237,13 +16237,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4066</v>
+        <v>0.4023</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16267,7 +16267,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4623</v>
+        <v>0.5062</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>116</v>
+        <v>-103</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16369,10 +16369,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5377000000000001</v>
+        <v>0.4938</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-116</v>
+        <v>103</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>115</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.4956</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>102</v>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5044</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>-102</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5041</v>
+        <v>0.5056</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>-102</v>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16633,13 +16633,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4959</v>
+        <v>0.4944</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>102</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16699,13 +16699,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5636</v>
+        <v>0.6298</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-129</v>
+        <v>-170</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-120</v>
+        <v>108</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 63.0% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16765,10 +16765,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4364</v>
+        <v>0.3702</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>105</v>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 37.0% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16963,13 +16963,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4302</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17029,13 +17029,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5698</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17091,17 +17091,17 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.441</v>
+        <v>0.3584</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-110</v>
+        <v>117</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17157,14 +17157,14 @@
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4757</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>110</v>
+        <v>-179</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>115</v>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17227,10 +17227,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4765</v>
+        <v>0.4786</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>113</v>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17293,13 +17293,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5235</v>
+        <v>0.5214</v>
       </c>
       <c r="G106" s="14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H106" s="15" t="n">
         <v>-110</v>
-      </c>
-      <c r="H106" s="15" t="n">
-        <v>-113</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17359,13 +17359,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5094</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-101</v>
+        <v>-104</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17425,13 +17425,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4985000000000001</v>
+        <v>0.4906</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17455,7 +17455,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17491,13 +17491,13 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.6222</v>
+        <v>0.6209</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-165</v>
+        <v>-164</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-195</v>
+        <v>-190</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17557,10 +17557,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.3778</v>
+        <v>0.3791</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>165</v>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.38</v>
+        <v>0.3771</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>127</v>
@@ -17653,7 +17653,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17689,13 +17689,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.62</v>
+        <v>0.6229</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-163</v>
+        <v>-165</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17755,10 +17755,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4958</v>
+        <v>0.5016</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>102</v>
+        <v>-101</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>-105</v>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4139</v>
+        <v>0.4081</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17887,10 +17887,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4124</v>
+        <v>0.4142</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>160</v>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17953,13 +17953,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5876</v>
+        <v>0.5858</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-142</v>
+        <v>-141</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-170</v>
+        <v>-165</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17983,7 +17983,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18151,13 +18151,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5256</v>
+        <v>0.5101</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-111</v>
+        <v>-104</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-106</v>
+        <v>105</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18181,7 +18181,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18217,13 +18217,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4744</v>
+        <v>0.4899</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18283,10 +18283,10 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5766</v>
+        <v>0.5815</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-136</v>
+        <v>-139</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>-130</v>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4234</v>
+        <v>0.4185</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18547,10 +18547,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.453</v>
+        <v>0.4251</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>104</v>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5469999999999999</v>
+        <v>0.5749</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-121</v>
+        <v>-135</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>110</v>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18679,10 +18679,10 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.409</v>
+        <v>0.4066</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>140</v>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18745,10 +18745,10 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.591</v>
+        <v>0.5933999999999999</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-144</v>
+        <v>-146</v>
       </c>
       <c r="H128" s="15" t="n">
         <v>-145</v>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.51</v>
+        <v>0.5114</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>-105</v>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -19005,13 +19005,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.49</v>
+        <v>0.4886</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19331,13 +19331,13 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5162</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>-110</v>
+        <v>117</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19397,10 +19397,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.4838</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>100</v>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19463,7 +19463,7 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5628</v>
+        <v>0.5641</v>
       </c>
       <c r="G139" s="14" t="n">
         <v>-129</v>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19529,13 +19529,13 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4372</v>
+        <v>0.4359</v>
       </c>
       <c r="G140" s="14" t="n">
         <v>129</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -20120,10 +20120,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7178</v>
+        <v>0.7188</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-254</v>
+        <v>-256</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-233</v>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.8% (fair -254). Your call.</t>
+          <t>Model 71.9% (fair -256). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20186,13 +20186,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2822</v>
+        <v>0.2812</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 28.2% (fair +254). Your call.</t>
+          <t>Model 28.1% (fair +256). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5291</v>
+        <v>0.5833957033370806</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-112</v>
+        <v>-140</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>113</v>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20714,13 +20714,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4709</v>
+        <v>0.4166042966629194</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-108</v>
+        <v>-103</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -20744,7 +20744,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20786,7 +20786,7 @@
         <v>-153</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -20912,13 +20912,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4448</v>
+        <v>0.4391</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20978,13 +20978,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5552</v>
+        <v>0.5609</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -21044,13 +21044,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5686</v>
+        <v>0.5735</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -21074,7 +21074,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.4% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21110,10 +21110,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4314</v>
+        <v>0.4265</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.6% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3287474</v>
+        <v>0.3895999999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 32.9% (fair +204). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -21374,10 +21374,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6712526</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-204</v>
+        <v>-157</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-122</v>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 67.1% (fair -204). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -21568,17 +21568,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -2.5</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5558</v>
+        <v>0.5719</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-125</v>
+        <v>-134</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -21634,14 +21634,14 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty +2.5</t>
+          <t>New York Liberty +1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4442</v>
+        <v>0.4281</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>100</v>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -21704,13 +21704,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.1925</v>
+        <v>0.1840000000000001</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>525</v>
+        <v>614</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 19.2% (fair +419). Your call.</t>
+          <t>Model 18.4% (fair +443). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.8075</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-419</v>
+        <v>-443</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-567</v>
@@ -21800,7 +21800,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 80.8% (fair -419). Your call.</t>
+          <t>Model 81.6% (fair -443). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -21968,13 +21968,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3926414967183107</v>
+        <v>0.4337</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22034,13 +22034,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6073585032816893</v>
+        <v>0.5663</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-155</v>
+        <v>-131</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -22100,13 +22100,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.2169</v>
+        <v>0.2205</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 21.7% (fair +361). Your call.</t>
+          <t>Model 22.1% (fair +354). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -22166,13 +22166,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.7831</v>
+        <v>0.7795</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-361</v>
+        <v>-354</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-413</v>
+        <v>-425</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 78.3% (fair -361). Your call.</t>
+          <t>Model 78.0% (fair -354). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>

--- a/data/output/workbook/2026-07-10.xlsx
+++ b/data/output/workbook/2026-07-10.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10 15:46</t>
+          <t>2026-07-10 17:16</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6783,246 +6783,167 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Athletics offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.704</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.146000000000001</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.6</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.854</v>
+        <v>4.704</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.062</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7086,22 +7007,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.062</v>
+        <v>7.854</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.625</v>
+        <v>1.062</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -7165,313 +7086,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>7.938</v>
+        <v>1.062</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.625</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.593</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.544</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Athletics defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.753</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>5.282</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.753</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>6.7</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>5.282</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.354</v>
+        <v>7.792</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7535,22 +7456,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.271</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>9.208</v>
+        <v>1.354</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -7614,72 +7535,151 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>1.271</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.582</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J82" s="36" t="inlineStr">
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.728</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7698,7 +7698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7715,171 +7715,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Texas Rangers defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.892</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.892</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>5.167</v>
+        <v>8.083</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.284</v>
+        <v>7.673</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7943,22 +8022,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.673</v>
+        <v>1.163</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -8022,317 +8101,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.163</v>
+        <v>8.571</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.679</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.767</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.571</v>
+        <v>0.79</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Houston Astros defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.193</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>5.012</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.193</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>7.816</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.033</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.012</v>
+        <v>7.625</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.816</v>
+        <v>1.041</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -8396,22 +8475,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.625</v>
+        <v>1.292</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.041</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -8475,147 +8554,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.292</v>
+        <v>8.417</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.592000000000001</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.593</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.417</v>
+        <v>0.642</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8988,10 +8988,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6166</v>
+        <v>0.6083000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5977</v>
+        <v>0.6005</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9101,32 +9101,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5601</v>
+        <v>0.6563</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-127</v>
+        <v>-191</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9177,22 +9177,22 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6233</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-190</v>
+        <v>-165</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9228,7 +9228,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9238,27 +9238,27 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6214999999999999</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-164</v>
+        <v>-174</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 63.6% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9294,17 +9294,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.5753</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-179</v>
+        <v>-135</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9360,37 +9360,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Atlanta Dream</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.1840000000000001</v>
+        <v>0.5473</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>443</v>
+        <v>-121</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>614</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 18.4% (fair +443). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9426,17 +9426,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9446,17 +9446,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6298</v>
+        <v>0.5919</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-170</v>
+        <v>-145</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9497,12 +9497,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Golden State Valkyries @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Over 154.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5801000000000001</v>
+        <v>0.5718</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-138</v>
+        <v>-134</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9578,17 +9578,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5801000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-125</v>
+        <v>-138</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5712</v>
+        <v>0.5544</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-133</v>
+        <v>-124</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9690,17 +9690,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9710,14 +9710,14 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5717</v>
+        <v>0.5469999999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-133</v>
+        <v>-121</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>115</v>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9761,12 +9761,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9776,14 +9776,14 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Over 177.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.571</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-147</v>
+        <v>-133</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9822,17 +9822,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9842,17 +9842,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.5179</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-135</v>
+        <v>-107</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9888,37 +9888,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4399</v>
+        <v>0.5062</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>127</v>
+        <v>-103</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9954,17 +9954,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9974,17 +9974,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5179</v>
+        <v>0.5396</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-107</v>
+        <v>-117</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10020,37 +10020,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Toronto Tempo</t>
+          <t>New York Liberty @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Toronto Tempo</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.288</v>
+        <v>0.5719</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>247</v>
+        <v>-134</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>300</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 28.8% (fair +247). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5305</v>
+        <v>0.5164</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>117</v>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10152,17 +10152,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5735</v>
+        <v>0.5162</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-134</v>
+        <v>-107</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -134). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10218,17 +10218,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>New York Liberty @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10238,17 +10238,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4658</v>
+        <v>0.6095</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>115</v>
+        <v>-156</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>144</v>
+        <v>-120</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10289,32 +10289,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5062</v>
+        <v>0.625</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-103</v>
+        <v>-167</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>122</v>
+        <v>-127</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10350,37 +10350,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Minnesota Lynx</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5719</v>
+        <v>0.5012</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-134</v>
+        <v>-100</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-104</v>
+        <v>122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10416,37 +10416,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5162</v>
+        <v>0.3995</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-107</v>
+        <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4589</v>
+        <v>0.459</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>118</v>
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5411</v>
+        <v>0.541</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-118</v>
@@ -10779,13 +10779,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5092</v>
+        <v>0.4988</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4908</v>
+        <v>0.5012</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>104</v>
+        <v>-100</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>122</v>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10911,10 +10911,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4023</v>
+        <v>0.3995</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10977,13 +10977,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5977</v>
+        <v>0.6005</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11043,13 +11043,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4251</v>
+        <v>0.428</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.572</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-117</v>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11175,13 +11175,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5717</v>
+        <v>0.5544</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-133</v>
+        <v>-124</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -133). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11241,10 +11241,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4283</v>
+        <v>0.4456</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>105</v>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +133). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11307,10 +11307,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4399</v>
+        <v>0.3897</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>170</v>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5601</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-127</v>
+        <v>-157</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>168</v>
+        <v>-178</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5342</v>
+        <v>0.440076</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-115</v>
+        <v>127</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-144</v>
+        <v>105</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4658</v>
+        <v>0.559924</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>115</v>
+        <v>-127</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11571,13 +11571,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4052</v>
+        <v>0.4081</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11637,13 +11637,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.5919</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11703,13 +11703,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5617</v>
+        <v>0.5639</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11769,10 +11769,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4383</v>
+        <v>0.4361</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>108</v>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11835,13 +11835,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4149</v>
+        <v>0.4041</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11901,13 +11901,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5851</v>
+        <v>0.5959</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-141</v>
+        <v>-147</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-134</v>
+        <v>-144</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -12039,7 +12039,7 @@
         <v>-138</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4243</v>
+        <v>0.4257</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>138</v>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5757</v>
+        <v>0.5743</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-141</v>
+        <v>-138</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12231,13 +12231,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5278</v>
+        <v>0.5262</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4722</v>
+        <v>0.4738</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>104</v>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5205</v>
+        <v>0.5184</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -109). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4795</v>
+        <v>0.4816</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>-108</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +109). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5726</v>
+        <v>0.5722</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>-134</v>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4274</v>
+        <v>0.4278</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>134</v>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4683</v>
+        <v>0.4645</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12693,10 +12693,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5317</v>
+        <v>0.5355</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-111</v>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12765,7 +12765,7 @@
         <v>107</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12831,7 +12831,7 @@
         <v>-107</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4524</v>
+        <v>0.454</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13089,10 +13089,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5476</v>
+        <v>0.546</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>-113</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13155,13 +13155,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5712</v>
+        <v>0.5753</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-133</v>
+        <v>-135</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13221,13 +13221,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4288</v>
+        <v>0.4247</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3834</v>
+        <v>0.3917</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>180</v>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6166</v>
+        <v>0.6083000000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>178</v>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13419,13 +13419,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4252</v>
+        <v>0.4254</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>135</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5748</v>
+        <v>0.5746</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-135</v>
@@ -13551,13 +13551,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3443</v>
+        <v>0.3437</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13617,13 +13617,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6563</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-190</v>
+        <v>-191</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13683,13 +13683,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3785</v>
+        <v>0.3767</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6214999999999999</v>
+        <v>0.6233</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13821,7 +13821,7 @@
         <v>286</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13887,7 +13887,7 @@
         <v>-286</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13947,13 +13947,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5564</v>
+        <v>0.5473</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-125</v>
+        <v>-121</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14013,13 +14013,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4436</v>
+        <v>0.4527</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14079,13 +14079,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4394</v>
+        <v>0.4503</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14145,13 +14145,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5606</v>
+        <v>0.5497000000000001</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-128</v>
+        <v>-122</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-141</v>
+        <v>-132</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5212</v>
+        <v>0.5125</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-109</v>
+        <v>-105</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14277,13 +14277,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4788</v>
+        <v>0.4875</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5065</v>
+        <v>0.5183</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-103</v>
+        <v>-108</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14409,13 +14409,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4935</v>
+        <v>0.4817</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5927</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>-133</v>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14541,13 +14541,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4073</v>
+        <v>0.4046999999999999</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4251</v>
+        <v>0.4282</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.5718</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-135</v>
+        <v>-134</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14735,10 +14735,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5152</v>
+        <v>0.5276</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-106</v>
+        <v>-112</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14799,10 +14799,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4848</v>
+        <v>0.4724</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.3631</v>
+        <v>0.4183</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.6369</v>
+        <v>0.5817</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-175</v>
+        <v>-139</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3379</v>
+        <v>0.3532</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>163</v>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 35.3% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6621</v>
+        <v>0.6468</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-196</v>
+        <v>-183</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-163</v>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 64.7% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15385,7 +15385,7 @@
         <v>-114</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5305</v>
+        <v>0.5164</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>117</v>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15577,13 +15577,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4695</v>
+        <v>0.4836</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15643,13 +15643,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5859</v>
+        <v>0.5849</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>-141</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-165</v>
+        <v>-163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4141</v>
+        <v>0.4151</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>141</v>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15907,13 +15907,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5099</v>
+        <v>0.5139</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15973,10 +15973,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4901</v>
+        <v>0.4861</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-108</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16039,13 +16039,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3801</v>
+        <v>0.3861</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16069,7 +16069,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6199</v>
+        <v>0.6139</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-163</v>
+        <v>-159</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-160</v>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16171,13 +16171,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5977</v>
+        <v>0.5567800000000001</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-149</v>
+        <v>-126</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-163</v>
+        <v>105</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16237,13 +16237,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4023</v>
+        <v>0.44322</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16267,7 +16267,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4956</v>
+        <v>0.4929</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>100</v>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5044</v>
+        <v>0.5071</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-110</v>
+        <v>-114</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.6298</v>
+        <v>0.5396</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-170</v>
+        <v>-117</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>108</v>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.3702</v>
+        <v>0.4604</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16831,13 +16831,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5828</v>
+        <v>0.5795</v>
       </c>
       <c r="G99" s="14" t="n">
+        <v>-138</v>
+      </c>
+      <c r="H99" s="15" t="n">
         <v>-140</v>
-      </c>
-      <c r="H99" s="15" t="n">
-        <v>-145</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16897,13 +16897,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4172</v>
+        <v>0.4205</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16963,10 +16963,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4302</v>
+        <v>0.43</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>127</v>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17029,10 +17029,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5698</v>
+        <v>0.57</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-133</v>
@@ -17059,7 +17059,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17095,10 +17095,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.3584</v>
+        <v>0.3644</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>117</v>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 36.4% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-179</v>
+        <v>-174</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 63.6% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17227,13 +17227,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4786</v>
+        <v>0.4839</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17293,13 +17293,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5214</v>
+        <v>0.5161</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17623,13 +17623,13 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.3771</v>
+        <v>0.375</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17653,7 +17653,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 37.5% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17689,10 +17689,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.6229</v>
+        <v>0.625</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-165</v>
+        <v>-167</v>
       </c>
       <c r="H112" s="15" t="n">
         <v>-127</v>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17755,13 +17755,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.5016</v>
+        <v>0.5102</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>-101</v>
+        <v>-104</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4081</v>
+        <v>0.4018</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17887,13 +17887,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4142</v>
+        <v>0.414</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17953,13 +17953,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5858</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-165</v>
+        <v>-170</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17983,7 +17983,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5164</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-108</v>
+        <v>-107</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>-122</v>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18085,13 +18085,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4814</v>
+        <v>0.4836</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18151,10 +18151,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5101</v>
+        <v>0.5211</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-104</v>
+        <v>-109</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>105</v>
@@ -18181,7 +18181,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18217,13 +18217,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4899</v>
+        <v>0.4789</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>100</v>
+        <v>-101</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18283,13 +18283,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5815</v>
+        <v>0.5858</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-139</v>
+        <v>-141</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-130</v>
+        <v>-140</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18349,10 +18349,10 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4185</v>
+        <v>0.4142</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>130</v>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18547,13 +18547,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4251</v>
+        <v>0.453</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18613,13 +18613,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5749</v>
+        <v>0.5469999999999999</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-135</v>
+        <v>-121</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18679,10 +18679,10 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4066</v>
+        <v>0.4056</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>140</v>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18745,13 +18745,13 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5933999999999999</v>
+        <v>0.5944</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-145</v>
+        <v>-155</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.4% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18939,13 +18939,13 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.5114</v>
+        <v>0.5128</v>
       </c>
       <c r="G131" s="14" t="n">
         <v>-105</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -19005,13 +19005,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4886</v>
+        <v>0.4872</v>
       </c>
       <c r="G132" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-108</v>
+        <v>-101</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19077,7 +19077,7 @@
         <v>173</v>
       </c>
       <c r="H133" s="15" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.4996</v>
+        <v>0.4997</v>
       </c>
       <c r="G141" s="14" t="n">
         <v>100</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.5004</v>
+        <v>0.5003</v>
       </c>
       <c r="G142" s="14" t="n">
         <v>-100</v>
@@ -20120,13 +20120,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7188</v>
+        <v>0.74107</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-256</v>
+        <v>-286</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-233</v>
+        <v>-115</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 71.9% (fair -256). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20186,13 +20186,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2812</v>
+        <v>0.25893</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 28.1% (fair +256). Your call.</t>
+          <t>Model 25.9% (fair +286). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -20252,13 +20252,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6534700194739194</v>
+        <v>0.5718</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-189</v>
+        <v>-134</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -189). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -20318,10 +20318,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3465299805260806</v>
+        <v>0.4282</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -20348,7 +20348,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +189). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -20516,13 +20516,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.712</v>
+        <v>0.67647</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-247</v>
+        <v>-209</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-285</v>
+        <v>-115</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 71.2% (fair -247). Your call.</t>
+          <t>Model 67.6% (fair -209). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -20582,10 +20582,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.288</v>
+        <v>0.32353</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>300</v>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 28.8% (fair +247). Your call.</t>
+          <t>Model 32.4% (fair +209). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -20644,17 +20644,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 180</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5833957033370806</v>
+        <v>0.5718854686460328</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-140</v>
+        <v>-134</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20710,17 +20710,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 180</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4166042966629194</v>
+        <v>0.4050145313539671</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-103</v>
+        <v>-106</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -20744,7 +20744,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -21044,13 +21044,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5735</v>
+        <v>0.571</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -21074,7 +21074,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -134). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21110,10 +21110,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4265</v>
+        <v>0.429</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>100</v>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +134). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -21308,10 +21308,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3895999999999999</v>
+        <v>0.3905</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>122</v>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -21374,13 +21374,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6095</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-157</v>
+        <v>-156</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -21704,10 +21704,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.1840000000000001</v>
+        <v>0.2266114000000001</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>443</v>
+        <v>341</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>614</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 18.4% (fair +443). Your call.</t>
+          <t>Model 22.7% (fair +341). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -21770,13 +21770,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.7733885999999999</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-443</v>
+        <v>-341</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-567</v>
+        <v>-115</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -21800,7 +21800,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 81.6% (fair -443). Your call.</t>
+          <t>Model 77.3% (fair -341). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -21968,13 +21968,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.3926414967183107</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 39.3% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22034,10 +22034,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.6073585032816893</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-131</v>
+        <v>-155</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-108</v>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 60.7% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -22100,10 +22100,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.2205</v>
+        <v>0.24286</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>400</v>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 22.1% (fair +354). Your call.</t>
+          <t>Model 24.3% (fair +312). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -22166,13 +22166,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.7795</v>
+        <v>0.75714</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-354</v>
+        <v>-312</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-425</v>
+        <v>-110</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 78.0% (fair -354). Your call.</t>
+          <t>Model 75.7% (fair -312). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>

--- a/data/output/workbook/2026-07-10.xlsx
+++ b/data/output/workbook/2026-07-10.xlsx
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10887075"/>
+    <ext cx="10125075" cy="10458450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10 17:16</t>
+          <t>2026-07-10 19:10</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3055,167 +3055,246 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs Cincinnati Reds defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>5.833</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.638</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.833</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>18th</t>
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.233</v>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.638</v>
+        <v>8.106</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>1.104</v>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
@@ -3279,22 +3358,22 @@
         </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.106</v>
+        <v>1.383</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.104</v>
+        <v>8.458</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -3358,313 +3437,313 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>1.383</v>
+        <v>7.404</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.45</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.404</v>
+        <v>0.532</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Chicago Cubs defense</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>3.987</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>3.987</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>7.404</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.767</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.753</v>
+        <v>7.896</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.404</v>
+        <v>1.213</v>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
@@ -3728,22 +3807,22 @@
         </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.896</v>
+        <v>1.354</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.213</v>
+        <v>9.532</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -3807,147 +3886,68 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>1.354</v>
+        <v>7.708</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>9.532</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.532</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.267</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.708</v>
+        <v>0.425</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4894,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4911,167 +4911,246 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Miami Marlins defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>3.633</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.929</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>3.633</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>7.735</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>3.7</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.289</v>
+        <v>7.694</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.735</v>
+        <v>0.959</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5135,22 +5214,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.694</v>
+        <v>1.082</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.959</v>
+        <v>8</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -5214,317 +5293,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.082</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.506</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.333</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>0.593</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Cleveland Guardians defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.131</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.723</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.133</v>
+        <v>8.286</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.131</v>
+        <v>7.939</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.286</v>
+        <v>0.918</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5588,22 +5667,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.939</v>
+        <v>1.143</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.918</v>
+        <v>7.816</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -5667,147 +5746,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.143</v>
+        <v>9.388</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.593</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.433</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>9.388</v>
+        <v>0.37</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5826,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,171 +5843,329 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs New York Mets defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.253</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.849</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.918</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.253</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.933</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.1</v>
+        <v>0.739</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.849</v>
+        <v>0.918</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.304</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6071,396 +6229,396 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.918</v>
+        <v>9.061</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.372</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.733</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.918</v>
+        <v>0.524</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.239000000000001</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>9.061</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Boston Red Sox defense</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.391</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.093</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>1st</t>
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>3.5</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.038</v>
+        <v>1.217</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.306</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6524,230 +6682,72 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.391</v>
+        <v>8.587</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.549</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.4</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.217</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>8.587</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6766,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6783,167 +6783,325 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Athletics offense vs Chicago White Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Athletics offense vs Chicago White Sox defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.704</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>8.146000000000001</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>1.062</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.5</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.704</v>
+        <v>1.062</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.146000000000001</v>
+        <v>8.625</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7007,392 +7165,392 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.854</v>
+        <v>7.938</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.593</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.5669999999999999</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.062</v>
+        <v>0.544</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.625</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.938</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Chicago White Sox offense vs Athletics defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Chicago White Sox offense vs Athletics defense</t>
+      <c r="K77" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>5.282</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.311999999999999</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.753</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
+        <v>1.354</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>6.7</v>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.282</v>
+        <v>1.271</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.792</v>
+        <v>9.208</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7456,230 +7614,72 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.354</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.582</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.733</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.271</v>
+        <v>0.728</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>9.208</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>8.146000000000001</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8862,7 +8862,7 @@
         <v>-177</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8898,17 +8898,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Texas Rangers</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6335999999999999</v>
+        <v>0.6177</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-173</v>
+        <v>-162</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8964,17 +8964,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Houston Astros @ Texas Rangers</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6083000000000001</v>
+        <v>0.6335999999999999</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-155</v>
+        <v>-173</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6005</v>
+        <v>0.5997</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>-150</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9101,32 +9101,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6563</v>
+        <v>0.5634</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-191</v>
+        <v>-129</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9186,13 +9186,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6233</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-165</v>
+        <v>-168</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9228,17 +9228,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ New York Mets</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9248,17 +9248,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6355999999999999</v>
+        <v>0.5981000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-174</v>
+        <v>-149</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -174). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9294,17 +9294,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Boston Red Sox @ New York Mets</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5753</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-135</v>
+        <v>-174</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 63.6% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.5777</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-121</v>
+        <v>-137</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9431,32 +9431,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5919</v>
+        <v>0.4366</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-145</v>
+        <v>129</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9492,17 +9492,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries @ Connecticut Sun</t>
+          <t>Kansas City Royals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 154.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5718</v>
+        <v>0.5469999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-134</v>
+        <v>-121</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Cleveland Guardians @ Miami Marlins</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9578,17 +9578,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5801000000000001</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-138</v>
+        <v>-118</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5544</v>
+        <v>0.5826</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-124</v>
+        <v>-140</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9690,17 +9690,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Baltimore Orioles</t>
+          <t>Chicago Sky @ Los Angeles Sparks</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9710,17 +9710,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 177.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5469999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-121</v>
+        <v>-133</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9761,12 +9761,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Los Angeles Sparks</t>
+          <t>Golden State Valkyries @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9776,17 +9776,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 154</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.571</v>
+        <v>0.5756</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9822,17 +9822,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Tampa Bay Rays</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9842,17 +9842,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5179</v>
+        <v>0.5377000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-107</v>
+        <v>-116</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Washington Nationals</t>
+          <t>Chicago Cubs @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9908,17 +9908,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5062</v>
+        <v>0.5319</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-103</v>
+        <v>-114</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9969,22 +9969,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5396</v>
+        <v>0.5962</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-117</v>
+        <v>-148</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>-108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10020,37 +10020,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Minnesota Lynx</t>
+          <t>Seattle Mariners @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5719</v>
+        <v>0.5179</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-134</v>
+        <v>-107</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-104</v>
+        <v>120</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10091,29 +10091,29 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Chicago White Sox</t>
+          <t>Portland Fire @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Portland Fire +12.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5164</v>
+        <v>0.5235000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-107</v>
+        <v>-110</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>117</v>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10157,32 +10157,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Cincinnati Reds</t>
+          <t>New York Liberty @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5162</v>
+        <v>0.5804</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-107</v>
+        <v>-138</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>117</v>
+        <v>-105</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10218,17 +10218,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Minnesota Lynx</t>
+          <t>New York Yankees @ Washington Nationals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10238,17 +10238,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6095</v>
+        <v>0.471</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-156</v>
+        <v>112</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-120</v>
+        <v>140</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10284,37 +10284,37 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.625</v>
+        <v>0.4947</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-167</v>
+        <v>102</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-127</v>
+        <v>128</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Milwaukee Brewers @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10370,17 +10370,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5012</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-100</v>
+        <v>-129</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10416,37 +10416,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Detroit Tigers</t>
+          <t>Athletics @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3995</v>
+        <v>0.5164</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>150</v>
+        <v>-107</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.459</v>
+        <v>0.4599</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.541</v>
+        <v>0.5401</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-108</v>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10779,13 +10779,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4988</v>
+        <v>0.4947</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5012</v>
+        <v>0.5053000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3995</v>
+        <v>0.4003</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>150</v>
@@ -10977,13 +10977,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6005</v>
+        <v>0.5997</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-150</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11043,13 +11043,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.428</v>
+        <v>0.4294</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.572</v>
+        <v>0.5706</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11175,13 +11175,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5544</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-124</v>
+        <v>-129</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11241,13 +11241,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4456</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11307,13 +11307,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3897</v>
+        <v>0.4366</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6103000000000001</v>
+        <v>0.5634</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-157</v>
+        <v>-129</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-178</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.440076</v>
+        <v>0.529</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>127</v>
+        <v>-112</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>105</v>
+        <v>-135</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.559924</v>
+        <v>0.471</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-127</v>
+        <v>112</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11571,10 +11571,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4081</v>
+        <v>0.4019</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>117</v>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11637,13 +11637,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5919</v>
+        <v>0.5981000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-145</v>
+        <v>-149</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11703,13 +11703,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5639</v>
+        <v>0.5629</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>-129</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11769,7 +11769,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4361</v>
+        <v>0.4371</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>129</v>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11835,13 +11835,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4041</v>
+        <v>0.3587399999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +147). Your call.</t>
+          <t>Model 35.9% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11901,13 +11901,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5959</v>
+        <v>0.6412600000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-147</v>
+        <v>-179</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-144</v>
+        <v>-105</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 64.1% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11967,13 +11967,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4199</v>
+        <v>0.4223</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5801000000000001</v>
+        <v>0.5777</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-138</v>
+        <v>-137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12099,13 +12099,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4257</v>
+        <v>0.4319</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12165,13 +12165,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5743</v>
+        <v>0.5681</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12231,13 +12231,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5262</v>
+        <v>0.5345</v>
       </c>
       <c r="G29" s="14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H29" s="15" t="n">
         <v>-111</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>-104</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12297,13 +12297,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4738</v>
+        <v>0.4655</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5184</v>
+        <v>0.5138</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12429,13 +12429,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4816</v>
+        <v>0.4862</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12495,13 +12495,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5722</v>
+        <v>0.5678</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-134</v>
+        <v>-131</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12561,13 +12561,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4278</v>
+        <v>0.4322</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.4528</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12693,13 +12693,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5472</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-115</v>
+        <v>-121</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-111</v>
+        <v>-121</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12765,7 +12765,7 @@
         <v>107</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12831,7 +12831,7 @@
         <v>-107</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12897,7 +12897,7 @@
         <v>177</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12963,7 +12963,7 @@
         <v>-177</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.454</v>
+        <v>0.4494</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13089,13 +13089,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.546</v>
+        <v>0.5506</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-120</v>
+        <v>-123</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13155,13 +13155,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5753</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-135</v>
+        <v>-118</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13221,13 +13221,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4247</v>
+        <v>0.4592000000000001</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13287,13 +13287,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3917</v>
+        <v>0.3823</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13353,13 +13353,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6083000000000001</v>
+        <v>0.6177</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-155</v>
+        <v>-162</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4254</v>
+        <v>0.4288</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>135</v>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13485,13 +13485,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5746</v>
+        <v>0.5712</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-138</v>
+        <v>-132</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13547,17 +13547,17 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3437</v>
+        <v>0.5053</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>191</v>
+        <v>-102</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +191). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13613,17 +13613,17 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6563</v>
+        <v>0.4947</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-191</v>
+        <v>102</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3767</v>
+        <v>0.3725</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>156</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 37.2% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6233</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-165</v>
+        <v>-168</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13821,7 +13821,7 @@
         <v>286</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13943,17 +13943,17 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5473</v>
+        <v>0.5826</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-121</v>
+        <v>-140</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14009,17 +14009,17 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4527</v>
+        <v>0.4174</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14079,13 +14079,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4503</v>
+        <v>0.4581</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14145,13 +14145,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5497000000000001</v>
+        <v>0.5419</v>
       </c>
       <c r="G58" s="14" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H58" s="15" t="n">
         <v>-122</v>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>-132</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14343,10 +14343,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5183</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-108</v>
+        <v>-126</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>100</v>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14409,13 +14409,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4817</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-102</v>
+        <v>119</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14475,13 +14475,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5917</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-133</v>
+        <v>-130</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14541,13 +14541,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4046999999999999</v>
+        <v>0.4083</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4282</v>
+        <v>0.4132</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14671,10 +14671,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5718</v>
+        <v>0.5868</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-134</v>
+        <v>-142</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5276</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>-112</v>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4724</v>
+        <v>0.4713</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>112</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14863,10 +14863,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4195</v>
+        <v>0.4434</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +138). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14927,10 +14927,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5805</v>
+        <v>0.5566</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-138</v>
+        <v>-126</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14991,10 +14991,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4183</v>
+        <v>0.4024</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.5976</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-139</v>
+        <v>-149</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15119,10 +15119,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5063</v>
+        <v>0.4994</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15183,10 +15183,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4937</v>
+        <v>0.5006</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>103</v>
+        <v>-100</v>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15247,13 +15247,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3532</v>
+        <v>0.3464</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 35.3% (fair +183). Your call.</t>
+          <t>Model 34.6% (fair +189). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6468</v>
+        <v>0.6536</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-183</v>
+        <v>-189</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>-163</v>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 64.7% (fair -183). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15643,13 +15643,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5849</v>
+        <v>0.5838</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-163</v>
+        <v>-160</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15709,10 +15709,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4151</v>
+        <v>0.4162</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>145</v>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15907,10 +15907,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5139</v>
+        <v>0.5125</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>100</v>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15973,13 +15973,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4861</v>
+        <v>0.4875</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16039,10 +16039,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3861</v>
+        <v>0.3843</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>150</v>
@@ -16069,7 +16069,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16105,13 +16105,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6139</v>
+        <v>0.6157</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-160</v>
+        <v>-165</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5062</v>
+        <v>0.4623</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-103</v>
+        <v>116</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16369,10 +16369,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4938</v>
+        <v>0.5377000000000001</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>103</v>
+        <v>-116</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>115</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16435,10 +16435,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4929</v>
+        <v>0.4955</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>100</v>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5071</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-114</v>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16567,10 +16567,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5056</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>-113</v>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16633,13 +16633,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4944</v>
+        <v>0.4904</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16699,13 +16699,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5396</v>
+        <v>0.5422</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4604</v>
+        <v>0.4578</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16831,13 +16831,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5795</v>
+        <v>0.5962</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-138</v>
+        <v>-148</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-140</v>
+        <v>-108</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16897,10 +16897,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4205</v>
+        <v>0.4038</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>126</v>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -17491,13 +17491,13 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.6209</v>
+        <v>0.6222</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>-190</v>
+        <v>-195</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17557,10 +17557,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.3791</v>
+        <v>0.3778</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>165</v>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5164</v>
+        <v>0.5147999999999999</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18085,13 +18085,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4836</v>
+        <v>0.4852</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18151,10 +18151,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5211</v>
+        <v>0.5236</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>105</v>
@@ -18181,7 +18181,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18217,13 +18217,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4789</v>
+        <v>0.4764</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-101</v>
+        <v>102</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18283,13 +18283,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5858</v>
+        <v>0.5915</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-141</v>
+        <v>-145</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-140</v>
+        <v>-145</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4142</v>
+        <v>0.4085</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18415,10 +18415,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.42</v>
+        <v>0.4172</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>138</v>
@@ -18445,7 +18445,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18481,13 +18481,13 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.58</v>
+        <v>0.5828</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-138</v>
+        <v>-140</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18553,7 +18553,7 @@
         <v>121</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18939,10 +18939,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.5128</v>
+        <v>0.5137</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>100</v>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -19005,13 +19005,13 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4872</v>
+        <v>0.4863</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-101</v>
+        <v>100</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.5956</v>
+        <v>0.5958</v>
       </c>
       <c r="G135" s="14" t="n">
         <v>-147</v>
@@ -19267,7 +19267,7 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.4045</v>
+        <v>0.4042</v>
       </c>
       <c r="G136" s="14" t="n">
         <v>147</v>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19331,10 +19331,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5162</v>
+        <v>0.5319</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-107</v>
+        <v>-114</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>117</v>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19397,13 +19397,13 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4838</v>
+        <v>0.4681</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19463,13 +19463,13 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5641</v>
+        <v>0.5657</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>-155</v>
+        <v>-160</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19529,10 +19529,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4359</v>
+        <v>0.4343</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>140</v>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -20192,7 +20192,7 @@
         <v>286</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -20248,17 +20248,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 154.5</t>
+          <t>Over 154</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5718</v>
+        <v>0.5756</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-134</v>
+        <v>-136</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -20314,14 +20314,14 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 154.5</t>
+          <t>Under 154</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4282</v>
+        <v>0.403</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>100</v>
@@ -20348,7 +20348,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -20456,7 +20456,7 @@
         <v>-301</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -20644,17 +20644,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 180</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5718854686460328</v>
+        <v>0.5833957033370806</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-134</v>
+        <v>-140</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -20710,17 +20710,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 180</t>
+          <t>Under 179.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4050145313539671</v>
+        <v>0.4166042966629194</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -20744,7 +20744,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -20786,7 +20786,7 @@
         <v>-153</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -20852,7 +20852,7 @@
         <v>153</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -20912,10 +20912,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4391</v>
+        <v>0.4418</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>113</v>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -20978,13 +20978,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5609</v>
+        <v>0.5582</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-128</v>
+        <v>-126</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3905</v>
+        <v>0.3287474</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -21338,7 +21338,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 32.9% (fair +204). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -21374,13 +21374,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6095</v>
+        <v>0.6712526</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-156</v>
+        <v>-204</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -21436,17 +21436,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 172.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4971</v>
+        <v>0.459</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -21502,17 +21502,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 172.5</t>
+          <t>Under 175.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5029</v>
+        <v>0.5409999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-101</v>
+        <v>-118</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -21572,13 +21572,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5719</v>
+        <v>0.5804</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-134</v>
+        <v>-138</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -21638,13 +21638,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4281</v>
+        <v>0.4196</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -21964,17 +21964,17 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream -13.5</t>
+          <t>Atlanta Dream -12.5</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3926414967183107</v>
+        <v>0.4765</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>122</v>
+        <v>-108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22030,17 +22030,17 @@
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Portland Fire +12.5</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6073585032816893</v>
+        <v>0.5235000000000001</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-155</v>
+        <v>-110</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -22172,7 +22172,7 @@
         <v>-312</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
